--- a/Passwords for SikhsinIndia.xlsx
+++ b/Passwords for SikhsinIndia.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
   <si>
     <t>SikhsinINDIA@gmail.com</t>
   </si>
@@ -122,12 +122,41 @@
   <si>
     <t>"Sikhs in UAE" Team</t>
   </si>
+  <si>
+    <t>Big/Major Cities of Madhya Pradesh in alphabetic order with h2 tags</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">We humbly request Sangat to share </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>details of Gurudwaras</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Name, City, Religious Importance &amp; Photographs) that are not yet listed on th website. Please email information on SikhsinIndia@gmail.com Your contributions will be well appreciated.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -160,6 +189,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -624,7 +661,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:E18"/>
+  <dimension ref="B2:E26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -684,6 +721,16 @@
       </c>
       <c r="C18" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3">
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3">
+      <c r="B26" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/Passwords for SikhsinIndia.xlsx
+++ b/Passwords for SikhsinIndia.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>SikhsinINDIA@gmail.com</t>
   </si>
@@ -150,6 +150,9 @@
       </rPr>
       <t xml:space="preserve"> (Name, City, Religious Importance &amp; Photographs) that are not yet listed on th website. Please email information on SikhsinIndia@gmail.com Your contributions will be well appreciated.</t>
     </r>
+  </si>
+  <si>
+    <t>https://granthsahib.wordpress.com/gurbani-pdf-files/</t>
   </si>
 </sst>
 </file>
@@ -661,7 +664,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B2:E26"/>
+  <dimension ref="B2:E29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="23.85546875" bestFit="1" customWidth="1"/>
@@ -731,6 +734,11 @@
     <row r="26" spans="2:3">
       <c r="B26" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3">
+      <c r="B29" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/Passwords for SikhsinIndia.xlsx
+++ b/Passwords for SikhsinIndia.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Database" sheetId="2" r:id="rId2"/>
     <sheet name="Email" sheetId="3" r:id="rId3"/>
+    <sheet name="Github" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
   <si>
     <t>SikhsinINDIA@gmail.com</t>
   </si>
@@ -154,12 +155,60 @@
   <si>
     <t>https://granthsahib.wordpress.com/gurbani-pdf-files/</t>
   </si>
+  <si>
+    <t>rgb(255,153,51)</t>
+  </si>
+  <si>
+    <t>git init</t>
+  </si>
+  <si>
+    <t>git remote add origin https://github.com/your-username/your-repo-name.git</t>
+  </si>
+  <si>
+    <t>git add .</t>
+  </si>
+  <si>
+    <t>git commit -m "Your commit message"</t>
+  </si>
+  <si>
+    <t>git branch -M main</t>
+  </si>
+  <si>
+    <t>git push -u origin main</t>
+  </si>
+  <si>
+    <t>git push</t>
+  </si>
+  <si>
+    <t>git remote remove origin</t>
+  </si>
+  <si>
+    <t>git remote add origin https://github.com/sikhsuae/SikhsUAE.git</t>
+  </si>
+  <si>
+    <t>ssh-keygen -t ed25519 -C "your_email@example.com"</t>
+  </si>
+  <si>
+    <t>ssh-keygen -t ed25519 -C "sikhsuae@gmail.com"</t>
+  </si>
+  <si>
+    <t>git remote set-url origin git@github.com:sikhsuae/SikhsUAE.git</t>
+  </si>
+  <si>
+    <t>Your public key has been saved in C:\Users\Hp/.ssh/id_ed25519.pub</t>
+  </si>
+  <si>
+    <t>The key fingerprint is:</t>
+  </si>
+  <si>
+    <t>SHA256:wbuOSI3dqF3PVu4hXFqGOhhJUKmUYCJ+wX4WlqL8F34 sikhsuae@gmail.com</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +250,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -226,7 +281,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -243,6 +298,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -718,6 +774,11 @@
         <v>7</v>
       </c>
     </row>
+    <row r="16" spans="2:5">
+      <c r="B16" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
         <v>9</v>
@@ -877,4 +938,109 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B3:B32"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="3" spans="2:2">
+      <c r="B3" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2">
+      <c r="B5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2">
+      <c r="B6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="2:2">
+      <c r="B7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="2:2">
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="2:2">
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="2:2">
+      <c r="B12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="2:2">
+      <c r="B14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="2:2">
+      <c r="B16" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="18" spans="2:2">
+      <c r="B18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="2:2">
+      <c r="B21" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" spans="2:2">
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="2:2">
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2">
+      <c r="B26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2">
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2">
+      <c r="B28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2">
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2">
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2">
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Passwords for SikhsinIndia.xlsx
+++ b/Passwords for SikhsinIndia.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
   <si>
     <t>SikhsinINDIA@gmail.com</t>
   </si>
@@ -202,6 +202,33 @@
   </si>
   <si>
     <t>SHA256:wbuOSI3dqF3PVu4hXFqGOhhJUKmUYCJ+wX4WlqL8F34 sikhsuae@gmail.com</t>
+  </si>
+  <si>
+    <t>rules_version = '2';</t>
+  </si>
+  <si>
+    <t>service cloud.firestore {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  match /databases/{database}/documents {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    // This matches any document in any collection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    match /{document=**} {</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      allow read, write: if true;  // WARNING: Open access (not secure)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  }</t>
+  </si>
+  <si>
+    <t>}</t>
   </si>
 </sst>
 </file>
@@ -817,12 +844,57 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B10"/>
+  <dimension ref="B10:B63"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="10" spans="2:2">
       <c r="B10" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="2:2">
+      <c r="B55" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="56" spans="2:2">
+      <c r="B56" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="57" spans="2:2">
+      <c r="B57" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="58" spans="2:2">
+      <c r="B58" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="2:2">
+      <c r="B59" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="60" spans="2:2">
+      <c r="B60" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="61" spans="2:2">
+      <c r="B61" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="62" spans="2:2">
+      <c r="B62" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="63" spans="2:2">
+      <c r="B63" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>

--- a/Passwords for SikhsinIndia.xlsx
+++ b/Passwords for SikhsinIndia.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
   <si>
     <t>SikhsinINDIA@gmail.com</t>
   </si>
@@ -229,13 +229,196 @@
   </si>
   <si>
     <t>}</t>
+  </si>
+  <si>
+    <r>
+      <t>City</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Faridabad"</t>
+    </r>
+  </si>
+  <si>
+    <t>(string)</t>
+  </si>
+  <si>
+    <r>
+      <t>Mobile</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"9718778983"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Bhai Ajeet Singh Ji"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Photo</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"./pictures/04_Sikh_Sevadars/13_Haryana/05_Faridabad/01_Bhai_Ajeet_Singh_Ji.jpg"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Specializes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Kirtani &amp; Pathi"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>State</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Haryana"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Video</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"https://www.youtube.com/watch?v=PSJVQKgOxSM"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>City</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"SAS Nagar"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Prabh Aasra"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>State</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Chandigarh"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"Home For Helpless"</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Webpage</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>"05_05_Prabh Aasra_SAS Nagar.html"</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -283,6 +466,12 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -308,7 +497,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -326,6 +515,9 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -844,7 +1036,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B10:B63"/>
+  <dimension ref="B10:B90"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="10" spans="2:2">
@@ -897,12 +1089,128 @@
         <v>55</v>
       </c>
     </row>
+    <row r="65" spans="2:2">
+      <c r="B65" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="66" spans="2:2">
+      <c r="B66" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="67" spans="2:2">
+      <c r="B67" s="9" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="68" spans="2:2">
+      <c r="B68" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="69" spans="2:2">
+      <c r="B69" s="9" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="70" spans="2:2">
+      <c r="B70" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="71" spans="2:2">
+      <c r="B71" s="9" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="72" spans="2:2">
+      <c r="B72" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="73" spans="2:2">
+      <c r="B73" s="9" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="74" spans="2:2">
+      <c r="B74" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="75" spans="2:2">
+      <c r="B75" s="9" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="76" spans="2:2">
+      <c r="B76" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="77" spans="2:2">
+      <c r="B77" s="9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="81" spans="2:2">
+      <c r="B81" s="9" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="82" spans="2:2">
+      <c r="B82" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="83" spans="2:2">
+      <c r="B83" s="9" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="84" spans="2:2">
+      <c r="B84" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="85" spans="2:2">
+      <c r="B85" s="9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="86" spans="2:2">
+      <c r="B86" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="87" spans="2:2">
+      <c r="B87" s="9" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="88" spans="2:2">
+      <c r="B88" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="89" spans="2:2">
+      <c r="B89" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="90" spans="2:2">
+      <c r="B90" t="s">
+        <v>57</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="B10" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 

--- a/Passwords for SikhsinIndia.xlsx
+++ b/Passwords for SikhsinIndia.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="1"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Database" sheetId="2" r:id="rId2"/>
     <sheet name="Email" sheetId="3" r:id="rId3"/>
     <sheet name="Github" sheetId="4" r:id="rId4"/>
+    <sheet name="You Tube" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
@@ -642,6 +643,51 @@
         <a:xfrm>
           <a:off x="3048000" y="1143000"/>
           <a:ext cx="10563225" cy="5019675"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1025" name="Picture 1"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="12734925" cy="5724525"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1423,4 +1469,14 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/Passwords for SikhsinIndia.xlsx
+++ b/Passwords for SikhsinIndia.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="4"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Passwords for SikhsinIndia.xlsx
+++ b/Passwords for SikhsinIndia.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -12,13 +12,14 @@
     <sheet name="Email" sheetId="3" r:id="rId3"/>
     <sheet name="Github" sheetId="4" r:id="rId4"/>
     <sheet name="You Tube" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="175">
   <si>
     <t>SikhsinINDIA@gmail.com</t>
   </si>
@@ -414,12 +415,330 @@
       <t>"05_05_Prabh Aasra_SAS Nagar.html"</t>
     </r>
   </si>
+  <si>
+    <t>Bhai Bhag Singh</t>
+  </si>
+  <si>
+    <t>Bhai Dilbag Singh</t>
+  </si>
+  <si>
+    <t>Bhai Mann Singh</t>
+  </si>
+  <si>
+    <t>Bhai Nidhan Singh</t>
+  </si>
+  <si>
+    <t>Bhai Kharbara Singh</t>
+  </si>
+  <si>
+    <t>Bhai Darbara Singh</t>
+  </si>
+  <si>
+    <t>Bhai Dyal Singh</t>
+  </si>
+  <si>
+    <t>Bhai Nihal Singh</t>
+  </si>
+  <si>
+    <t>Bhai Budh Singh</t>
+  </si>
+  <si>
+    <t>Bhai Gurbaksh Singh</t>
+  </si>
+  <si>
+    <t>Bhai Sukha Singh</t>
+  </si>
+  <si>
+    <t>Bhai Mehar Singh</t>
+  </si>
+  <si>
+    <t>Bhai Lachhmi Singh</t>
+  </si>
+  <si>
+    <t>Bhai Pirthi Singh</t>
+  </si>
+  <si>
+    <t>Bhai Sham Singh</t>
+  </si>
+  <si>
+    <t>Bhai Gurmukh Singh</t>
+  </si>
+  <si>
+    <t>Bhai Lachhmi Chand</t>
+  </si>
+  <si>
+    <t>Bhai Daya Singh</t>
+  </si>
+  <si>
+    <t>Bhai Jiwan Singh</t>
+  </si>
+  <si>
+    <t>Bhai Bhagwan Singh</t>
+  </si>
+  <si>
+    <t>Bhai Fateh Singh</t>
+  </si>
+  <si>
+    <t>Bhai Meharban Singh</t>
+  </si>
+  <si>
+    <t>Bhai Gurdas Singh</t>
+  </si>
+  <si>
+    <t>Bhai Sahib Singh</t>
+  </si>
+  <si>
+    <t>Bhai Sadhu Singh</t>
+  </si>
+  <si>
+    <t>Bhai Dhanna Singh</t>
+  </si>
+  <si>
+    <t>(40) Bhai Mahan Singh</t>
+  </si>
+  <si>
+    <t>(01</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Bhag Singh</t>
+  </si>
+  <si>
+    <t>(02</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Dilbag Singh</t>
+  </si>
+  <si>
+    <t>(03</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Mann Singh</t>
+  </si>
+  <si>
+    <t>(04</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Nidhan Singh</t>
+  </si>
+  <si>
+    <t>(05</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Kharbara Singh</t>
+  </si>
+  <si>
+    <t>(06</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Darbara Singh</t>
+  </si>
+  <si>
+    <t>(07</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Dyal Singh</t>
+  </si>
+  <si>
+    <t>(08</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Nihal Singh</t>
+  </si>
+  <si>
+    <t>(09</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Khushal Singh</t>
+  </si>
+  <si>
+    <t>(10</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Ganda Singh</t>
+  </si>
+  <si>
+    <t>(11</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Ishmer Singh</t>
+  </si>
+  <si>
+    <t>(12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Singha</t>
+  </si>
+  <si>
+    <t>(13</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Bhalla Singh</t>
+  </si>
+  <si>
+    <t>(14</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Suhel Singh</t>
+  </si>
+  <si>
+    <t>(15</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Chamba Singh</t>
+  </si>
+  <si>
+    <t>(16</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Ganga Singh</t>
+  </si>
+  <si>
+    <t>(17</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Sumer Singh</t>
+  </si>
+  <si>
+    <t>(18</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Sultan Singh</t>
+  </si>
+  <si>
+    <t>(19</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Maya Singh</t>
+  </si>
+  <si>
+    <t>(20</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Massa Singh</t>
+  </si>
+  <si>
+    <t>(21</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Sarja Singh</t>
+  </si>
+  <si>
+    <t>(22</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Sadhu Singh</t>
+  </si>
+  <si>
+    <t>(23</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Gulab Singh</t>
+  </si>
+  <si>
+    <t>(24</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Harsa Singh</t>
+  </si>
+  <si>
+    <t>(25</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Sangat Singh</t>
+  </si>
+  <si>
+    <t>(26</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Hari Singh</t>
+  </si>
+  <si>
+    <t>(27</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Dhana Singh</t>
+  </si>
+  <si>
+    <t>(28</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Karam Singh</t>
+  </si>
+  <si>
+    <t>(29</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Kirt Singh</t>
+  </si>
+  <si>
+    <t>(30</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Lachman Singh</t>
+  </si>
+  <si>
+    <t>(31</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Buddha Singh</t>
+  </si>
+  <si>
+    <t>(32</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Kesho Singh</t>
+  </si>
+  <si>
+    <t>(33</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Jado Singh</t>
+  </si>
+  <si>
+    <t>(34</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Sobha Singh</t>
+  </si>
+  <si>
+    <t>(35</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Bhanga Singh</t>
+  </si>
+  <si>
+    <t>(36</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Joga Singh</t>
+  </si>
+  <si>
+    <t>(37</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Dharam Singh</t>
+  </si>
+  <si>
+    <t>(38</t>
+  </si>
+  <si>
+    <t>(39</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Kala Singh</t>
+  </si>
+  <si>
+    <t>(40</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Bhai Mahan Singh</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,6 +792,18 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF333333"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF353C41"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -498,7 +829,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
@@ -518,6 +849,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1479,4 +1816,462 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="C1:F81"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="6" max="6" width="19.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:6">
+      <c r="E1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="3:6">
+      <c r="F2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="3:6" ht="44.25">
+      <c r="C3" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F3" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="3:6" ht="44.25">
+      <c r="C4" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="5" spans="3:6" ht="44.25">
+      <c r="C5" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F5" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="6" spans="3:6" ht="44.25">
+      <c r="C6" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="3:6" ht="58.5">
+      <c r="C7" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="8" spans="3:6" ht="58.5">
+      <c r="C8" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" spans="3:6" ht="44.25">
+      <c r="C9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="F9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="3:6" ht="44.25">
+      <c r="C10" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11" spans="3:6" ht="44.25">
+      <c r="C11" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="3:6" ht="58.5">
+      <c r="C12" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="13" spans="3:6" ht="44.25">
+      <c r="C13" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="14" spans="3:6" ht="44.25">
+      <c r="C14" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F14" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="3:6" ht="58.5">
+      <c r="C15" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="F15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="3:6" ht="44.25">
+      <c r="C16" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="F16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6" ht="44.25">
+      <c r="C17" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="18" spans="3:6" ht="58.5">
+      <c r="C18" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>128</v>
+      </c>
+      <c r="F18" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="3:6" ht="58.5">
+      <c r="C19" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="3:6" ht="58.5">
+      <c r="C20" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F20" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6" ht="44.25">
+      <c r="C21" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="22" spans="3:6" ht="44.25">
+      <c r="C22" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F22" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6" ht="58.5">
+      <c r="C23" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6" ht="44.25">
+      <c r="C24" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>140</v>
+      </c>
+      <c r="F24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6" ht="58.5">
+      <c r="C25" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="F25" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6" ht="44.25">
+      <c r="C26" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6" ht="44.25">
+      <c r="C27" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="28" spans="3:6" ht="44.25">
+      <c r="C28" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="F28" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="3:6" ht="58.5">
+      <c r="C29" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F29" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="30" spans="3:6" ht="44.25">
+      <c r="C30" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F30" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="31" spans="3:6" ht="58.5">
+      <c r="C31" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F31" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="32" spans="3:6" ht="44.25">
+      <c r="C32" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="F32" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" ht="44.25">
+      <c r="C33" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="F33" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="34" spans="3:6" ht="44.25">
+      <c r="C34" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="F34" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="35" spans="3:6" ht="58.5">
+      <c r="C35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="F35" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6" ht="44.25">
+      <c r="C36" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F36" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" spans="3:6" ht="44.25">
+      <c r="C37" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="F37" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="38" spans="3:6" ht="58.5">
+      <c r="C38" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F38" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="39" spans="3:6" ht="58.5">
+      <c r="C39" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="F39" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="40" spans="3:6" ht="44.25">
+      <c r="C40" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="F40" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="41" spans="3:6" ht="44.25">
+      <c r="C41" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="F41" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="81" spans="5:5" ht="66">
+      <c r="E81" s="11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Passwords for SikhsinIndia.xlsx
+++ b/Passwords for SikhsinIndia.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="5"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/Passwords for SikhsinIndia.xlsx
+++ b/Passwords for SikhsinIndia.xlsx
@@ -45,9 +45,6 @@
     <t>Add styles to show the page and buttons in strictly two colors - yellow/orange (kesari) FF9933 and black color</t>
   </si>
   <si>
-    <t>Convert html file to have look and feel in  Add styles to show the page and buttons in strictly two colors - yellow/orange (kesari) FF9933 and black color</t>
-  </si>
-  <si>
     <t>FIREBASE</t>
   </si>
   <si>
@@ -732,6 +729,9 @@
   </si>
   <si>
     <t xml:space="preserve"> Bhai Mahan Singh</t>
+  </si>
+  <si>
+    <t>Convert html file to have look and feel in  Add styles to show the page and buttons in strictly two colors - yellow/orange (kesari) FF9933 and black color. Also make the html code mobile friendly</t>
   </si>
 </sst>
 </file>
@@ -1368,7 +1368,7 @@
     </row>
     <row r="14" spans="2:5" ht="17.25">
       <c r="B14" s="3" t="s">
-        <v>8</v>
+        <v>174</v>
       </c>
     </row>
     <row r="15" spans="2:5" ht="17.25">
@@ -1378,30 +1378,30 @@
     </row>
     <row r="16" spans="2:5">
       <c r="B16" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="21" spans="2:3">
       <c r="B21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26" spans="2:3">
       <c r="B26" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="2:3">
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1424,167 +1424,167 @@
   <sheetData>
     <row r="10" spans="2:2">
       <c r="B10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="55" spans="2:2">
       <c r="B55" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="2:2">
       <c r="B56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="57" spans="2:2">
       <c r="B57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58" spans="2:2">
       <c r="B58" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="59" spans="2:2">
       <c r="B59" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="60" spans="2:2">
       <c r="B60" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61" spans="2:2">
       <c r="B61" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62" spans="2:2">
       <c r="B62" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="63" spans="2:2">
       <c r="B63" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="2:2">
       <c r="B65" s="9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="66" spans="2:2">
       <c r="B66" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="67" spans="2:2">
       <c r="B67" s="9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="68" spans="2:2">
       <c r="B68" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="69" spans="2:2">
       <c r="B69" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="70" spans="2:2">
       <c r="B70" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71" spans="2:2">
       <c r="B71" s="9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="72" spans="2:2">
       <c r="B72" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="2:2">
       <c r="B73" s="9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="74" spans="2:2">
       <c r="B74" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="2:2">
       <c r="B75" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="2:2">
       <c r="B76" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77" spans="2:2">
       <c r="B77" s="9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="81" spans="2:2">
       <c r="B81" s="9" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="82" spans="2:2">
       <c r="B82" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83" spans="2:2">
       <c r="B83" s="9" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="84" spans="2:2">
       <c r="B84" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="85" spans="2:2">
       <c r="B85" s="9" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="86" spans="2:2">
       <c r="B86" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="2:2">
       <c r="B87" s="9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="2:2">
       <c r="B88" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="89" spans="2:2">
       <c r="B89" s="9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="90" spans="2:2">
       <c r="B90" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1612,17 +1612,17 @@
     </row>
     <row r="9" spans="2:4" ht="45.75">
       <c r="B9" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="243">
       <c r="B11" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="195.75">
       <c r="B13" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="2:4">
@@ -1630,67 +1630,67 @@
     </row>
     <row r="15" spans="2:4" ht="45.75">
       <c r="B15" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16" spans="2:4" ht="45.75">
       <c r="B16" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="2:2" ht="60.75">
       <c r="B17" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18" spans="2:2" ht="45.75">
       <c r="B18" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19" spans="2:2" ht="60.75">
       <c r="B19" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="2:2" ht="60.75">
       <c r="B20" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="2:2" ht="409.6">
       <c r="B22" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="24" spans="2:2" ht="390.75">
       <c r="B24" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="26" spans="2:2" ht="345.75">
       <c r="B26" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="2:2" ht="165.75">
       <c r="B28" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="30" spans="2:2" ht="240.75">
       <c r="B30" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32" spans="2:2" ht="45.75">
       <c r="B32" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="2:2" ht="63">
       <c r="B33" s="7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1710,97 +1710,97 @@
   <sheetData>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:2">
       <c r="B5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="2:2">
       <c r="B6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="2:2">
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="2:2">
       <c r="B9" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="2:2">
       <c r="B11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:2">
       <c r="B12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="2:2">
       <c r="B14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16" spans="2:2">
       <c r="B16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="2:2">
       <c r="B18" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="21" spans="2:2">
       <c r="B21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="22" spans="2:2">
       <c r="B22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="24" spans="2:2">
       <c r="B24" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="26" spans="2:2">
       <c r="B26" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="27" spans="2:2">
       <c r="B27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="2:2">
       <c r="B28" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="2:2">
       <c r="B30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" spans="2:2">
       <c r="B31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32" spans="2:2">
       <c r="B32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1828,446 +1828,446 @@
   <sheetData>
     <row r="1" spans="3:6">
       <c r="E1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="2" spans="3:6">
       <c r="F2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="3:6" ht="44.25">
       <c r="C3" s="10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E3" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="F3" t="s">
         <v>98</v>
-      </c>
-      <c r="F3" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="4" spans="3:6" ht="44.25">
       <c r="C4" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E4" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="F4" t="s">
         <v>100</v>
-      </c>
-      <c r="F4" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="5" spans="3:6" ht="44.25">
       <c r="C5" s="10" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F5" t="s">
         <v>102</v>
-      </c>
-      <c r="F5" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="6" spans="3:6" ht="44.25">
       <c r="C6" s="10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="F6" t="s">
         <v>104</v>
-      </c>
-      <c r="F6" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="7" spans="3:6" ht="58.5">
       <c r="C7" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E7" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" t="s">
         <v>106</v>
-      </c>
-      <c r="F7" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="8" spans="3:6" ht="58.5">
       <c r="C8" s="10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E8" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="F8" t="s">
         <v>108</v>
-      </c>
-      <c r="F8" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="9" spans="3:6" ht="44.25">
       <c r="C9" s="10" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E9" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" t="s">
         <v>110</v>
-      </c>
-      <c r="F9" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="10" spans="3:6" ht="44.25">
       <c r="C10" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E10" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F10" t="s">
         <v>112</v>
-      </c>
-      <c r="F10" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="11" spans="3:6" ht="44.25">
       <c r="C11" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E11" s="11" t="s">
+        <v>113</v>
+      </c>
+      <c r="F11" t="s">
         <v>114</v>
-      </c>
-      <c r="F11" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="12" spans="3:6" ht="58.5">
       <c r="C12" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="F12" t="s">
         <v>116</v>
-      </c>
-      <c r="F12" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="13" spans="3:6" ht="44.25">
       <c r="C13" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E13" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F13" t="s">
         <v>118</v>
-      </c>
-      <c r="F13" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="14" spans="3:6" ht="44.25">
       <c r="C14" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E14" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" t="s">
         <v>120</v>
-      </c>
-      <c r="F14" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="15" spans="3:6" ht="58.5">
       <c r="C15" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E15" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="F15" t="s">
         <v>122</v>
-      </c>
-      <c r="F15" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="16" spans="3:6" ht="44.25">
       <c r="C16" s="10" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E16" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" t="s">
         <v>124</v>
-      </c>
-      <c r="F16" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="17" spans="3:6" ht="44.25">
       <c r="C17" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E17" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="F17" t="s">
         <v>126</v>
-      </c>
-      <c r="F17" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="18" spans="3:6" ht="58.5">
       <c r="C18" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E18" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="F18" t="s">
         <v>128</v>
-      </c>
-      <c r="F18" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="19" spans="3:6" ht="58.5">
       <c r="C19" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E19" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" t="s">
         <v>130</v>
-      </c>
-      <c r="F19" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="20" spans="3:6" ht="58.5">
       <c r="C20" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E20" s="11" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" t="s">
         <v>132</v>
-      </c>
-      <c r="F20" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="21" spans="3:6" ht="44.25">
       <c r="C21" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E21" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="F21" t="s">
         <v>134</v>
-      </c>
-      <c r="F21" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="22" spans="3:6" ht="44.25">
       <c r="C22" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E22" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" t="s">
         <v>136</v>
-      </c>
-      <c r="F22" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="23" spans="3:6" ht="58.5">
       <c r="C23" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E23" s="11" t="s">
+        <v>137</v>
+      </c>
+      <c r="F23" t="s">
         <v>138</v>
-      </c>
-      <c r="F23" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="24" spans="3:6" ht="44.25">
       <c r="C24" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E24" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="F24" t="s">
         <v>140</v>
-      </c>
-      <c r="F24" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="25" spans="3:6" ht="58.5">
       <c r="C25" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E25" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="F25" t="s">
         <v>142</v>
-      </c>
-      <c r="F25" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="26" spans="3:6" ht="44.25">
       <c r="C26" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E26" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="F26" t="s">
         <v>144</v>
-      </c>
-      <c r="F26" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="27" spans="3:6" ht="44.25">
       <c r="C27" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E27" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="F27" t="s">
         <v>146</v>
-      </c>
-      <c r="F27" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="28" spans="3:6" ht="44.25">
       <c r="C28" s="10" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E28" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F28" t="s">
         <v>148</v>
-      </c>
-      <c r="F28" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="29" spans="3:6" ht="58.5">
       <c r="C29" s="10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E29" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="F29" t="s">
         <v>150</v>
-      </c>
-      <c r="F29" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="30" spans="3:6" ht="44.25">
       <c r="C30" s="10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E30" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="F30" t="s">
         <v>152</v>
-      </c>
-      <c r="F30" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="31" spans="3:6" ht="58.5">
       <c r="C31" s="10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E31" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="F31" t="s">
         <v>154</v>
-      </c>
-      <c r="F31" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="32" spans="3:6" ht="44.25">
       <c r="C32" s="10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E32" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="F32" t="s">
         <v>156</v>
-      </c>
-      <c r="F32" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="33" spans="3:6" ht="44.25">
       <c r="C33" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E33" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="F33" t="s">
         <v>158</v>
-      </c>
-      <c r="F33" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="34" spans="3:6" ht="44.25">
       <c r="C34" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E34" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F34" t="s">
         <v>160</v>
-      </c>
-      <c r="F34" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="35" spans="3:6" ht="58.5">
       <c r="C35" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E35" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="F35" t="s">
         <v>162</v>
-      </c>
-      <c r="F35" t="s">
-        <v>163</v>
       </c>
     </row>
     <row r="36" spans="3:6" ht="44.25">
       <c r="C36" s="10" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E36" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="F36" t="s">
         <v>164</v>
-      </c>
-      <c r="F36" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="37" spans="3:6" ht="44.25">
       <c r="C37" s="10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E37" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="F37" t="s">
         <v>166</v>
-      </c>
-      <c r="F37" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="38" spans="3:6" ht="58.5">
       <c r="C38" s="10" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E38" s="11" t="s">
+        <v>167</v>
+      </c>
+      <c r="F38" t="s">
         <v>168</v>
-      </c>
-      <c r="F38" t="s">
-        <v>169</v>
       </c>
     </row>
     <row r="39" spans="3:6" ht="58.5">
       <c r="C39" s="10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F39" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="40" spans="3:6" ht="44.25">
       <c r="C40" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E40" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="F40" t="s">
         <v>171</v>
-      </c>
-      <c r="F40" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="41" spans="3:6" ht="44.25">
       <c r="C41" s="10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E41" s="11" t="s">
+        <v>172</v>
+      </c>
+      <c r="F41" t="s">
         <v>173</v>
-      </c>
-      <c r="F41" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="81" spans="5:5" ht="66">
       <c r="E81" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
